--- a/tame_output/ON/bt/strategyON_20231109.xlsx
+++ b/tame_output/ON/bt/strategyON_20231109.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>88.7%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>79.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>20.5%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-20.3%</t>
+          <t>-20.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>11.6%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>102.6%</t>
+          <t>102.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1069,11 +1069,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-157.1%</t>
+          <t>-156.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>132.8%</t>
+          <t>132.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>25.5%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1775"/>
+  <dimension ref="A1:G1776"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42335,7 +42335,7 @@
         <v>45237</v>
       </c>
       <c r="B1775" t="n">
-        <v>3.085454620141824</v>
+        <v>3.087505451293021</v>
       </c>
       <c r="C1775" t="n">
         <v>3.05676708948516</v>
@@ -42351,6 +42351,29 @@
       </c>
       <c r="G1775" t="n">
         <v>4.362259752179861</v>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" s="2" t="n">
+        <v>45238</v>
+      </c>
+      <c r="B1776" t="n">
+        <v>3.122172992355287</v>
+      </c>
+      <c r="C1776" t="n">
+        <v>3.060334699322022</v>
+      </c>
+      <c r="D1776" t="n">
+        <v>1.540008791897969</v>
+      </c>
+      <c r="E1776" t="n">
+        <v>3.675981791767463</v>
+      </c>
+      <c r="F1776" t="n">
+        <v>2.175821104491166</v>
+      </c>
+      <c r="G1776" t="n">
+        <v>4.365827362016724</v>
       </c>
     </row>
   </sheetData>
